--- a/Budgeting System_Employee List.xlsx
+++ b/Budgeting System_Employee List.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oclpholdings-my.sharepoint.com/personal/jumalonpvp_ortigas_com_ph/Documents/Desktop/AI Claude/Budgeting System/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jumalonpvp\Downloads\Budgeting System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{603156FE-2D29-41BA-B186-E7EE61ADE963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409DB07B-47D9-44A5-868D-4F8D30250B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D1070E7B-5A73-493B-A95C-C89D80F0301C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{D1070E7B-5A73-493B-A95C-C89D80F0301C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Employee List" sheetId="1" r:id="rId1"/>
+    <sheet name="Role" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Employee List'!$A$1:$O$364</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4015" uniqueCount="1283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4389" uniqueCount="1661">
   <si>
     <t>Id Number</t>
   </si>
@@ -3888,13 +3892,1147 @@
   </si>
   <si>
     <t>2023-08-07</t>
+  </si>
+  <si>
+    <t>Roles</t>
+  </si>
+  <si>
+    <t>Budget Officer</t>
+  </si>
+  <si>
+    <t>BC&amp;A Head</t>
+  </si>
+  <si>
+    <t>Department Preparer</t>
+  </si>
+  <si>
+    <t>Centralized Department Preparer</t>
+  </si>
+  <si>
+    <t>Centralized Department Reviewer</t>
+  </si>
+  <si>
+    <t>Department Approver</t>
+  </si>
+  <si>
+    <t>Centralized Department Approver</t>
+  </si>
+  <si>
+    <t>CFO</t>
+  </si>
+  <si>
+    <t>Human Resources Manpower Preparer</t>
+  </si>
+  <si>
+    <t>Corporate Finance</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>Estates &amp; Offices Finance</t>
+  </si>
+  <si>
+    <t>Budget, Controls &amp; Analysis</t>
+  </si>
+  <si>
+    <t>Abegail V. Tuloza</t>
+  </si>
+  <si>
+    <t>Aliana Renee B. Ortonio</t>
+  </si>
+  <si>
+    <t>Andrei Paul C. Lustre</t>
+  </si>
+  <si>
+    <t>Angela Mariz C. Tarrobal</t>
+  </si>
+  <si>
+    <t>Angelica P. Romo</t>
+  </si>
+  <si>
+    <t>Anjelika J. Satorre</t>
+  </si>
+  <si>
+    <t>Anna Mariel Remedios A. Delfin</t>
+  </si>
+  <si>
+    <t>Anne Robert S. Dolleton</t>
+  </si>
+  <si>
+    <t>Arna Regina B. Mallari</t>
+  </si>
+  <si>
+    <t>Arvin John M. Pangiligan</t>
+  </si>
+  <si>
+    <t>Baby Jane P. Rejano</t>
+  </si>
+  <si>
+    <t>Bernadeth G. Garcia</t>
+  </si>
+  <si>
+    <t>Bheverly Ann C. Sespeñe</t>
+  </si>
+  <si>
+    <t>Carl-G Boie M. Ileto</t>
+  </si>
+  <si>
+    <t>Carlo M. Tenerife</t>
+  </si>
+  <si>
+    <t>Chantel Dominique B. Golfo</t>
+  </si>
+  <si>
+    <t>Cristine Joy M. Oxinio</t>
+  </si>
+  <si>
+    <t>Darlene P. Ancheta</t>
+  </si>
+  <si>
+    <t>David Jefferson F. Hanga-an</t>
+  </si>
+  <si>
+    <t>Denice Dimple F. Bentir</t>
+  </si>
+  <si>
+    <t>Destine M. Dimaculangan</t>
+  </si>
+  <si>
+    <t>Eleonor F. Honra</t>
+  </si>
+  <si>
+    <t>Eunice L. Balverde</t>
+  </si>
+  <si>
+    <t>Fritzie M. Panes</t>
+  </si>
+  <si>
+    <t>Hazelline Joy S. Goles</t>
+  </si>
+  <si>
+    <t>Ianne Ashley H. Del Rosario</t>
+  </si>
+  <si>
+    <t>Janicka Alecxie C. Javier</t>
+  </si>
+  <si>
+    <t>Jara Ivee R. Montenegro</t>
+  </si>
+  <si>
+    <t>Jayvee F. Rodriguez</t>
+  </si>
+  <si>
+    <t>Jerina Reine S. Peñaflor</t>
+  </si>
+  <si>
+    <t>Joanne P. Sardoma</t>
+  </si>
+  <si>
+    <t>John Patrick G. David</t>
+  </si>
+  <si>
+    <t>Joshua C. Cano</t>
+  </si>
+  <si>
+    <t>Jovelyn A. Duran</t>
+  </si>
+  <si>
+    <t>Kanda C. Ynion</t>
+  </si>
+  <si>
+    <t>Karyll Mae G. San Pedro</t>
+  </si>
+  <si>
+    <t>Kristine O. Joren</t>
+  </si>
+  <si>
+    <t>Kristofferson G. Rodriguez</t>
+  </si>
+  <si>
+    <t>Laarni Mae G. Tapang</t>
+  </si>
+  <si>
+    <t>Leah Mae C. Reyes</t>
+  </si>
+  <si>
+    <t>Lovely I. Lilangan</t>
+  </si>
+  <si>
+    <t>Ma. Lourdes S. Gumayan</t>
+  </si>
+  <si>
+    <t>Mac Joven M. Eleazar</t>
+  </si>
+  <si>
+    <t>Mae A. Asi</t>
+  </si>
+  <si>
+    <t>Marian Mae N. Bonacua</t>
+  </si>
+  <si>
+    <t>Martha Kristina N. Serquiña</t>
+  </si>
+  <si>
+    <t>Mary Joy F. Elizon</t>
+  </si>
+  <si>
+    <t>Michael Eduard K. Arroyo</t>
+  </si>
+  <si>
+    <t>Nicole B. Italia</t>
+  </si>
+  <si>
+    <t>Paulina Alexandra C. Aguilar</t>
+  </si>
+  <si>
+    <t>Princess Sarah J. Labong</t>
+  </si>
+  <si>
+    <t>Renelyn G. Octavo</t>
+  </si>
+  <si>
+    <t>Renie-Len M. Espiritu</t>
+  </si>
+  <si>
+    <t>Rhea B. Aclan</t>
+  </si>
+  <si>
+    <t>Rie Kim B. Dela Cruz</t>
+  </si>
+  <si>
+    <t>Rona May V. Diaz</t>
+  </si>
+  <si>
+    <t>Ryan Gil G. Moreno</t>
+  </si>
+  <si>
+    <t>Sara Jane F. Pantanilla</t>
+  </si>
+  <si>
+    <t>Sara Joy A. Barreno</t>
+  </si>
+  <si>
+    <t>Tristan O. Bucasas</t>
+  </si>
+  <si>
+    <t>Zabdiel Lyka Evanne C. Tosio</t>
+  </si>
+  <si>
+    <t>Abigail S. Agcaoili</t>
+  </si>
+  <si>
+    <t>Albert Philip Y. Penales</t>
+  </si>
+  <si>
+    <t>Andrea R. Tumambing</t>
+  </si>
+  <si>
+    <t>April Joy A. Natividad</t>
+  </si>
+  <si>
+    <t>Ariza S. Diaz</t>
+  </si>
+  <si>
+    <t>Arnel E. Samson</t>
+  </si>
+  <si>
+    <t>Arveen Dominic S. Calderon</t>
+  </si>
+  <si>
+    <t>Ashley Nicole M. Torres</t>
+  </si>
+  <si>
+    <t>Billy O. Elpedes</t>
+  </si>
+  <si>
+    <t>Camille Ann B. Reglos</t>
+  </si>
+  <si>
+    <t>Caroline C. Mejia</t>
+  </si>
+  <si>
+    <t>Caryn Sidney H. Baldivia</t>
+  </si>
+  <si>
+    <t>Celine Kate T. Celestial</t>
+  </si>
+  <si>
+    <t>Christine A. Laxamana</t>
+  </si>
+  <si>
+    <t>Cindy P. Solano</t>
+  </si>
+  <si>
+    <t>Dion Delano C. Averilla</t>
+  </si>
+  <si>
+    <t>Dominic Robert Ian T. Villanueva</t>
+  </si>
+  <si>
+    <t>Elizabeth C. Degullado</t>
+  </si>
+  <si>
+    <t>Emil Ray R. Rada</t>
+  </si>
+  <si>
+    <t>Flordeliza A. Ocba</t>
+  </si>
+  <si>
+    <t>Jalline A. Pebres</t>
+  </si>
+  <si>
+    <t>Jan Heribert A. Patinio</t>
+  </si>
+  <si>
+    <t>Jason C. Galang</t>
+  </si>
+  <si>
+    <t>Jennifer M. Cammayo</t>
+  </si>
+  <si>
+    <t>Jennifer M. Ringor</t>
+  </si>
+  <si>
+    <t>Jenny Marie R. Demore</t>
+  </si>
+  <si>
+    <t>Jercee P. Selda</t>
+  </si>
+  <si>
+    <t>Jewel Valerie R. Macaranas</t>
+  </si>
+  <si>
+    <t>Jill Noreen O. Ignacio</t>
+  </si>
+  <si>
+    <t>Johannah Pauline S. Gequillana</t>
+  </si>
+  <si>
+    <t>John Howard A. Garcia</t>
+  </si>
+  <si>
+    <t>John Mark A. Daymiel</t>
+  </si>
+  <si>
+    <t>John Michael M. Simon</t>
+  </si>
+  <si>
+    <t>John Steven G. Caballero</t>
+  </si>
+  <si>
+    <t>Joshua B. Mina</t>
+  </si>
+  <si>
+    <t>Joven C. Borjal</t>
+  </si>
+  <si>
+    <t>Joyce Ann A. Alicos</t>
+  </si>
+  <si>
+    <t>Julianne Denise A. Capitan</t>
+  </si>
+  <si>
+    <t>Jun Gerald A. Sioson</t>
+  </si>
+  <si>
+    <t>Kerstine Lee F. Forlales</t>
+  </si>
+  <si>
+    <t>Kimberly Grace A. Canumay</t>
+  </si>
+  <si>
+    <t>King Leonard Terence T. Arsolon</t>
+  </si>
+  <si>
+    <t>Krisha Mae A. Enriquez</t>
+  </si>
+  <si>
+    <t>Lorie May A. Briva</t>
+  </si>
+  <si>
+    <t>Ma. Dia Lauren C. Valenton</t>
+  </si>
+  <si>
+    <t>Maria Belinda B. Cledera</t>
+  </si>
+  <si>
+    <t>Maria Hanna E. Palconit</t>
+  </si>
+  <si>
+    <t>Marjorie B. Monteroso</t>
+  </si>
+  <si>
+    <t>Mark A. Puzon</t>
+  </si>
+  <si>
+    <t>Mark Anthony R. Sevilla</t>
+  </si>
+  <si>
+    <t>Mark Jason A. Baja</t>
+  </si>
+  <si>
+    <t>Mark Raven N. Alsola</t>
+  </si>
+  <si>
+    <t>Marlon L. Galang</t>
+  </si>
+  <si>
+    <t>Marlyn M. Fran</t>
+  </si>
+  <si>
+    <t>Marvin F. Paralejas</t>
+  </si>
+  <si>
+    <t>Marvin Christopher M. Llacuna</t>
+  </si>
+  <si>
+    <t>Mervin F. Frivaldo</t>
+  </si>
+  <si>
+    <t>Mhel C. Payongayong</t>
+  </si>
+  <si>
+    <t>Mike Ayo T. Mengullo</t>
+  </si>
+  <si>
+    <t>Myla M. De Jesus</t>
+  </si>
+  <si>
+    <t>Neil Christian D. Abenir</t>
+  </si>
+  <si>
+    <t>Noel A. So</t>
+  </si>
+  <si>
+    <t>Norman L. Ferreras</t>
+  </si>
+  <si>
+    <t>Patricia Antonette M. Dangan</t>
+  </si>
+  <si>
+    <t>Paul Adrian B. Javen</t>
+  </si>
+  <si>
+    <t>Pia Mae Q. Renolayan</t>
+  </si>
+  <si>
+    <t>Raphael Rosalio Martin T. Estrada</t>
+  </si>
+  <si>
+    <t>Razel Anne M. Villanueva</t>
+  </si>
+  <si>
+    <t>Reñiel F. Matining</t>
+  </si>
+  <si>
+    <t>Reymundo F. Hinquillo</t>
+  </si>
+  <si>
+    <t>Reynabeth E. Almoradie</t>
+  </si>
+  <si>
+    <t>Rowena D. Mislos</t>
+  </si>
+  <si>
+    <t>Shamina I. Campong</t>
+  </si>
+  <si>
+    <t>Shayne Marion C. Caday</t>
+  </si>
+  <si>
+    <t>Shiela B. Adorna</t>
+  </si>
+  <si>
+    <t>Tristan Jethro C. Elevado</t>
+  </si>
+  <si>
+    <t>Venus C. Apaya</t>
+  </si>
+  <si>
+    <t>Viel R. Echon</t>
+  </si>
+  <si>
+    <t>Vin-Mer Raphael M. Ramirez</t>
+  </si>
+  <si>
+    <t>Wendelyn E. Alcantara</t>
+  </si>
+  <si>
+    <t>Wilbert P. Dimzon</t>
+  </si>
+  <si>
+    <t>Alaiza B. Enriquez</t>
+  </si>
+  <si>
+    <t>Alben G. Corpin</t>
+  </si>
+  <si>
+    <t>Albertine Ellen R. Jimenez</t>
+  </si>
+  <si>
+    <t>Aldrian A. Esteban</t>
+  </si>
+  <si>
+    <t>Aldrin Son C. Palmos</t>
+  </si>
+  <si>
+    <t>Aldwin D. Cabatay</t>
+  </si>
+  <si>
+    <t>Alliah V. Villamor</t>
+  </si>
+  <si>
+    <t>Alona C. Agustin</t>
+  </si>
+  <si>
+    <t>Alvina Camille B. Eria</t>
+  </si>
+  <si>
+    <t>Amabelle P. Dizon</t>
+  </si>
+  <si>
+    <t>Anabelle P. Derilo</t>
+  </si>
+  <si>
+    <t>Andrea Julia P. Roque</t>
+  </si>
+  <si>
+    <t>Andrea Romina C. Macasero</t>
+  </si>
+  <si>
+    <t>Angelica E. Policarpio</t>
+  </si>
+  <si>
+    <t>Aries M. Caloyloy</t>
+  </si>
+  <si>
+    <t>Arnel B. Mata</t>
+  </si>
+  <si>
+    <t>Barry T. Dela Rosa</t>
+  </si>
+  <si>
+    <t>Benedict Nicholas A. Sandejas</t>
+  </si>
+  <si>
+    <t>Benjamin S. Borja</t>
+  </si>
+  <si>
+    <t>Betsy C. Macaraeg</t>
+  </si>
+  <si>
+    <t>Carlos Miguel F. Briones</t>
+  </si>
+  <si>
+    <t>Carol T. Mills</t>
+  </si>
+  <si>
+    <t>Carolina C. Tenedero</t>
+  </si>
+  <si>
+    <t>Caroline E. Bingabing</t>
+  </si>
+  <si>
+    <t>Catherine S. Dueñas</t>
+  </si>
+  <si>
+    <t>Ceasar D. Buenaventura</t>
+  </si>
+  <si>
+    <t>Celina M. Marcos</t>
+  </si>
+  <si>
+    <t>Charlene Angeli H. Jose</t>
+  </si>
+  <si>
+    <t>Chasty A. Villamin</t>
+  </si>
+  <si>
+    <t>Cheryl J. Panganiban</t>
+  </si>
+  <si>
+    <t>Chezzka Sheen P. Padilla-Ballungay</t>
+  </si>
+  <si>
+    <t>Christian Bernard B. Fulay</t>
+  </si>
+  <si>
+    <t>Claire B. Sayson</t>
+  </si>
+  <si>
+    <t>Clarissa S. Tabor</t>
+  </si>
+  <si>
+    <t>Dachel Marie F. Vigal</t>
+  </si>
+  <si>
+    <t>Davee M. Zuñiga</t>
+  </si>
+  <si>
+    <t>Desiree I. Toraldo</t>
+  </si>
+  <si>
+    <t>Diane Carina O. Mendoza</t>
+  </si>
+  <si>
+    <t>Earl Henry H. Sanchez</t>
+  </si>
+  <si>
+    <t>Edgar A. De Vera</t>
+  </si>
+  <si>
+    <t>Edlyn S. Viloria</t>
+  </si>
+  <si>
+    <t>Elias Isagani A. Elacio</t>
+  </si>
+  <si>
+    <t>Elida Vanessa D. Sunga</t>
+  </si>
+  <si>
+    <t>Elizabeth D. Rosario</t>
+  </si>
+  <si>
+    <t>Eloida O. Tubania</t>
+  </si>
+  <si>
+    <t>Emlin Mae D. Javillonar</t>
+  </si>
+  <si>
+    <t>Enrique E. Gutierrez</t>
+  </si>
+  <si>
+    <t>Erish Jordan M. Mariano</t>
+  </si>
+  <si>
+    <t>Fay Justine V. Bolisay</t>
+  </si>
+  <si>
+    <t>Franklin G. Estoy</t>
+  </si>
+  <si>
+    <t>Gamayca Q. Casem</t>
+  </si>
+  <si>
+    <t>Gemma A. Ramirez</t>
+  </si>
+  <si>
+    <t>Gerardo G. Amansec</t>
+  </si>
+  <si>
+    <t>Gonzalo Romualdo H. Sto. Domingo</t>
+  </si>
+  <si>
+    <t>Isaias R. Isanan</t>
+  </si>
+  <si>
+    <t>Ivy C. Bayrante</t>
+  </si>
+  <si>
+    <t>James Paul M. Dela Rea</t>
+  </si>
+  <si>
+    <t>Janeena Arielle Marie M. Lansangan</t>
+  </si>
+  <si>
+    <t>Janine G. Sampiano</t>
+  </si>
+  <si>
+    <t>Jasmin D. Mamauag</t>
+  </si>
+  <si>
+    <t>Javier D. Hernandez</t>
+  </si>
+  <si>
+    <t>Jay P. Toledo</t>
+  </si>
+  <si>
+    <t>Jazminne Joy B. Pante</t>
+  </si>
+  <si>
+    <t>Jean D. Leonor</t>
+  </si>
+  <si>
+    <t>Jenalyn C. Ruelo</t>
+  </si>
+  <si>
+    <t>Jennalyn J. Belardo</t>
+  </si>
+  <si>
+    <t>Jennifer I. Campaner</t>
+  </si>
+  <si>
+    <t>Jennifer R. Sison</t>
+  </si>
+  <si>
+    <t>Jennifer E. Vallecera</t>
+  </si>
+  <si>
+    <t>Jerome R. Gorospe</t>
+  </si>
+  <si>
+    <t>Jessie James L. Candelaria</t>
+  </si>
+  <si>
+    <t>Joana Marie A. Narvasa</t>
+  </si>
+  <si>
+    <t>Jocilyn A. Mendoza</t>
+  </si>
+  <si>
+    <t>Joey H. Lasanas</t>
+  </si>
+  <si>
+    <t>John G. Icay</t>
+  </si>
+  <si>
+    <t>John Carlo A. Zamora</t>
+  </si>
+  <si>
+    <t>John Carmelo L. Ledesma</t>
+  </si>
+  <si>
+    <t>John Fidel V. Lukinab</t>
+  </si>
+  <si>
+    <t>John Marco L. Wee</t>
+  </si>
+  <si>
+    <t>Jolene C. Espos-Noble</t>
+  </si>
+  <si>
+    <t>Jonagale O. De Guzman</t>
+  </si>
+  <si>
+    <t>Jonamie V. Albiad</t>
+  </si>
+  <si>
+    <t>Jonathan M. Fabricante</t>
+  </si>
+  <si>
+    <t>Jose B. Gutierrez</t>
+  </si>
+  <si>
+    <t>Jose Antonio III V. Evangelista</t>
+  </si>
+  <si>
+    <t>Jose Clyde Evans P. Solemne</t>
+  </si>
+  <si>
+    <t>Jose Emmanuel H. Jalandoni</t>
+  </si>
+  <si>
+    <t>Jose Gordon M. Gomez</t>
+  </si>
+  <si>
+    <t>Jose Rafael F. Diño</t>
+  </si>
+  <si>
+    <t>Judel M. Flores</t>
+  </si>
+  <si>
+    <t>Judelyn M. Relor</t>
+  </si>
+  <si>
+    <t>June Jesus F. Vazquez</t>
+  </si>
+  <si>
+    <t>Justine C. Abanador</t>
+  </si>
+  <si>
+    <t>Justine Alexandra M. Papa</t>
+  </si>
+  <si>
+    <t>Justine Bianca B. Lagman</t>
+  </si>
+  <si>
+    <t>Kaiza Azalea B. Rivera</t>
+  </si>
+  <si>
+    <t>Karen A. Encinas</t>
+  </si>
+  <si>
+    <t>Karlos Anthony P. Quilbio</t>
+  </si>
+  <si>
+    <t>Katherine A. Pacoma</t>
+  </si>
+  <si>
+    <t>Kathleen Halley L. Coneras</t>
+  </si>
+  <si>
+    <t>Kenry F. Navarro</t>
+  </si>
+  <si>
+    <t>Kimberly C. Alon</t>
+  </si>
+  <si>
+    <t>Krisha R. Eusebio</t>
+  </si>
+  <si>
+    <t>Kristine Mae P. Villegas</t>
+  </si>
+  <si>
+    <t>Kristine May O. Alcantara</t>
+  </si>
+  <si>
+    <t>Lea Fatima S. Sueño</t>
+  </si>
+  <si>
+    <t>Leansley G. Pascua</t>
+  </si>
+  <si>
+    <t>Lenny N. Catiis</t>
+  </si>
+  <si>
+    <t>Loida A. Peñaranda</t>
+  </si>
+  <si>
+    <t>Louis Ranier E. Concepcion</t>
+  </si>
+  <si>
+    <t>Luigie P. Magtuto</t>
+  </si>
+  <si>
+    <t>Ma. Aireen Jo H. Garcia</t>
+  </si>
+  <si>
+    <t>Ma. Charmaine T. De Castro</t>
+  </si>
+  <si>
+    <t>Ma. Karen I. Caparas</t>
+  </si>
+  <si>
+    <t>Ma. Katalina Isabela Y. Tayag</t>
+  </si>
+  <si>
+    <t>Ma. Renielda C. Bacani</t>
+  </si>
+  <si>
+    <t>Mailyn C. Esperano</t>
+  </si>
+  <si>
+    <t>Marco Apollo S. Enriquez</t>
+  </si>
+  <si>
+    <t>Margarita D. Bania</t>
+  </si>
+  <si>
+    <t>Maria Cristina V. Ferando</t>
+  </si>
+  <si>
+    <t>Maria Jasmin J. Badilla</t>
+  </si>
+  <si>
+    <t>Maria Jennifer J. Almojuela</t>
+  </si>
+  <si>
+    <t>Maria Katherine S. Salamat</t>
+  </si>
+  <si>
+    <t>Mariane V. Lopez</t>
+  </si>
+  <si>
+    <t>Marielle R. Quianzon</t>
+  </si>
+  <si>
+    <t>Marife C. Blaquera</t>
+  </si>
+  <si>
+    <t>Marilyn Z. Dacdac</t>
+  </si>
+  <si>
+    <t>Mark Christian R. Gotos</t>
+  </si>
+  <si>
+    <t>Mark Glenn F. Manuel</t>
+  </si>
+  <si>
+    <t>Mark Joseph A. Tubac</t>
+  </si>
+  <si>
+    <t>Marvin M. Mercado</t>
+  </si>
+  <si>
+    <t>Marvin David H. Satingin</t>
+  </si>
+  <si>
+    <t>Mary Grace R. Gagarin</t>
+  </si>
+  <si>
+    <t>Marybeth G. Monis</t>
+  </si>
+  <si>
+    <t>Mayca Joy M. Amante</t>
+  </si>
+  <si>
+    <t>McGlenn O. Darakan</t>
+  </si>
+  <si>
+    <t>Melanie Ann D. Bukuhan</t>
+  </si>
+  <si>
+    <t>Menchie T. Insigne</t>
+  </si>
+  <si>
+    <t>Michael David I. Abundo</t>
+  </si>
+  <si>
+    <t>Minchie Blaire G. Aungon</t>
+  </si>
+  <si>
+    <t>Monalisa V. Lauraya</t>
+  </si>
+  <si>
+    <t>Monique Leticia L. Castañeda</t>
+  </si>
+  <si>
+    <t>Naisa S. Reyes</t>
+  </si>
+  <si>
+    <t>Nanette C. Omadto</t>
+  </si>
+  <si>
+    <t>Nerissa D. Abejar</t>
+  </si>
+  <si>
+    <t>Nina Roxan A. Dela Cruz</t>
+  </si>
+  <si>
+    <t>Pauline Mae L. Daaca</t>
+  </si>
+  <si>
+    <t>Princess Vera P. Jumalon</t>
+  </si>
+  <si>
+    <t>Priscilla R. Magabilin</t>
+  </si>
+  <si>
+    <t>Quenee Ann L. Solidum</t>
+  </si>
+  <si>
+    <t>Ralph Jason U. Fajardo</t>
+  </si>
+  <si>
+    <t>Randyboy F. Torres</t>
+  </si>
+  <si>
+    <t>Raymond M. Santos</t>
+  </si>
+  <si>
+    <t>Rea Katherine C. Baylon</t>
+  </si>
+  <si>
+    <t>Reggie T. Acbang</t>
+  </si>
+  <si>
+    <t>Reneelyn A. Alcantara</t>
+  </si>
+  <si>
+    <t>Rey Harold C. Quijano</t>
+  </si>
+  <si>
+    <t>Reynaldo S. Lubalan</t>
+  </si>
+  <si>
+    <t>Rhiza B. Deocariza</t>
+  </si>
+  <si>
+    <t>Rhomel Y. Villarosa</t>
+  </si>
+  <si>
+    <t>Robert S. Lao</t>
+  </si>
+  <si>
+    <t>Rodolfo V. Lansangan</t>
+  </si>
+  <si>
+    <t>Ronald John O. Gregorio</t>
+  </si>
+  <si>
+    <t>Ronilo B. Quiat</t>
+  </si>
+  <si>
+    <t>Rosalie H. Bicera</t>
+  </si>
+  <si>
+    <t>Rosamond U. Villanueva</t>
+  </si>
+  <si>
+    <t>Rose Ann F. Estrada</t>
+  </si>
+  <si>
+    <t>Roselda D. Gonzales</t>
+  </si>
+  <si>
+    <t>Roselyn P. Jimenez</t>
+  </si>
+  <si>
+    <t>Ryan F. Del Rosario</t>
+  </si>
+  <si>
+    <t>Shane Eimeren B. Abalos</t>
+  </si>
+  <si>
+    <t>Sharieanne A. Tabilin</t>
+  </si>
+  <si>
+    <t>Sheila Marie S. Perez</t>
+  </si>
+  <si>
+    <t>Thomas Jason O. Dejoras</t>
+  </si>
+  <si>
+    <t>Victor Emmanuel B. Ahorro</t>
+  </si>
+  <si>
+    <t>William M. Simacon</t>
+  </si>
+  <si>
+    <t>Winnie T. Tumandao</t>
+  </si>
+  <si>
+    <t>Xantine Kristel C. Morales</t>
+  </si>
+  <si>
+    <t>Zoren Jacob S. Cabangis</t>
+  </si>
+  <si>
+    <t>Alexis C. Tecson</t>
+  </si>
+  <si>
+    <t>Angelique S. Mozo</t>
+  </si>
+  <si>
+    <t>Carmela S. Machuca</t>
+  </si>
+  <si>
+    <t>Charles Bryan D. Ramos</t>
+  </si>
+  <si>
+    <t>Chesca Marie V. Clariza</t>
+  </si>
+  <si>
+    <t>Christian Andrei D. Abenales</t>
+  </si>
+  <si>
+    <t>Dennis M. Perez</t>
+  </si>
+  <si>
+    <t>Eduardo M. Sacbibit</t>
+  </si>
+  <si>
+    <t>Eljay A. Serrano</t>
+  </si>
+  <si>
+    <t>Erika A. Posadas</t>
+  </si>
+  <si>
+    <t>Gian Carlo E. Liwag</t>
+  </si>
+  <si>
+    <t>Harvey Bryan R. Peralta</t>
+  </si>
+  <si>
+    <t>Isabel O. Garcia</t>
+  </si>
+  <si>
+    <t>Janica A. Apita</t>
+  </si>
+  <si>
+    <t>January P. Tuason</t>
+  </si>
+  <si>
+    <t>Jazmhin Ehlaiza L. Doroja</t>
+  </si>
+  <si>
+    <t>Jericho Z. Garde</t>
+  </si>
+  <si>
+    <t>Jessica P. Fernandez</t>
+  </si>
+  <si>
+    <t>Joan Camille R. Penuela</t>
+  </si>
+  <si>
+    <t>Jonnalyn P. Ayala</t>
+  </si>
+  <si>
+    <t>Joval Aaron C. Torres</t>
+  </si>
+  <si>
+    <t>Joyce Ann G. Dizon</t>
+  </si>
+  <si>
+    <t>Juan Antonio O. Dela Paz</t>
+  </si>
+  <si>
+    <t>Kate D. Sisio</t>
+  </si>
+  <si>
+    <t>Kher-Ann R. Mariano</t>
+  </si>
+  <si>
+    <t>Kristabelle T. Mendoza</t>
+  </si>
+  <si>
+    <t>Mariele Q. Angeles</t>
+  </si>
+  <si>
+    <t>Marvin B. Palacio</t>
+  </si>
+  <si>
+    <t>Niño Roy P. Canturias</t>
+  </si>
+  <si>
+    <t>Raoul S. Roldan</t>
+  </si>
+  <si>
+    <t>Rica M. De Leon</t>
+  </si>
+  <si>
+    <t>Sheena Lyn U. Ching</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Joy Fernando</t>
+  </si>
+  <si>
+    <t>Monica David</t>
+  </si>
+  <si>
+    <t>Carla Cianet Buenaobra</t>
+  </si>
+  <si>
+    <t>Rossel Locsin</t>
+  </si>
+  <si>
+    <t>Shaira Princess Tejada</t>
+  </si>
+  <si>
+    <t>Vanessa Openiano</t>
+  </si>
+  <si>
+    <t>Daisy Abendanio</t>
+  </si>
+  <si>
+    <t>Lee Rose Ollina</t>
+  </si>
+  <si>
+    <t>Renee Cajardo</t>
+  </si>
+  <si>
+    <t>Lindsay Claire Carreon</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3909,6 +5047,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3918,7 +5064,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3941,14 +5087,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4283,7 +5442,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F23702-AA52-4900-9029-87698A4EA02C}">
-  <dimension ref="A1:N364"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:O364"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -4294,15 +5454,16 @@
     <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="54.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="49.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.1796875" customWidth="1"/>
+    <col min="10" max="10" width="28.1796875" customWidth="1"/>
     <col min="11" max="11" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.453125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4345,8 +5506,11 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O1" s="4" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>2503008</v>
       </c>
@@ -4389,8 +5553,11 @@
       <c r="N2" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O2" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2501002</v>
       </c>
@@ -4433,8 +5600,11 @@
       <c r="N3" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O3" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2601003</v>
       </c>
@@ -4477,8 +5647,11 @@
       <c r="N4" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O4" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2602010</v>
       </c>
@@ -4521,8 +5694,11 @@
       <c r="N5" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O5" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>2212750</v>
       </c>
@@ -4565,8 +5741,11 @@
       <c r="N6" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O6" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>2506022</v>
       </c>
@@ -4609,8 +5788,11 @@
       <c r="N7" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O7" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>2106608</v>
       </c>
@@ -4653,8 +5835,11 @@
       <c r="N8" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O8" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>2512043</v>
       </c>
@@ -4697,8 +5882,11 @@
       <c r="N9" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O9" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>2510036</v>
       </c>
@@ -4741,8 +5929,11 @@
       <c r="N10" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O10" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>1907494</v>
       </c>
@@ -4785,8 +5976,11 @@
       <c r="N11" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O11" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>2002571</v>
       </c>
@@ -4829,8 +6023,11 @@
       <c r="N12" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O12" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>2309870</v>
       </c>
@@ -4873,8 +6070,11 @@
       <c r="N13" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O13" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>2109627</v>
       </c>
@@ -4917,8 +6117,11 @@
       <c r="N14" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O14" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>2602009</v>
       </c>
@@ -4961,8 +6164,11 @@
       <c r="N15" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O15" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>2011584</v>
       </c>
@@ -5005,8 +6211,11 @@
       <c r="N16" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O16" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>2312898</v>
       </c>
@@ -5049,8 +6258,11 @@
       <c r="N17" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O17" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>2303787</v>
       </c>
@@ -5093,8 +6305,11 @@
       <c r="N18" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O18" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>2409976</v>
       </c>
@@ -5137,8 +6352,11 @@
       <c r="N19" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O19" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>2111644</v>
       </c>
@@ -5181,8 +6399,11 @@
       <c r="N20" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O20" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>2204693</v>
       </c>
@@ -5225,8 +6446,11 @@
       <c r="N21" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O21" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>2507027</v>
       </c>
@@ -5269,8 +6493,11 @@
       <c r="N22" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O22" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>2507026</v>
       </c>
@@ -5313,8 +6540,11 @@
       <c r="N23" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O23" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>2104602</v>
       </c>
@@ -5357,8 +6587,11 @@
       <c r="N24" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O24" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>2311896</v>
       </c>
@@ -5401,8 +6634,11 @@
       <c r="N25" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O25" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2601004</v>
       </c>
@@ -5445,8 +6681,11 @@
       <c r="N26" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O26" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>2512044</v>
       </c>
@@ -5489,8 +6728,11 @@
       <c r="N27" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O27" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2506024</v>
       </c>
@@ -5533,8 +6775,11 @@
       <c r="N28" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O28" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>2303793</v>
       </c>
@@ -5577,8 +6822,11 @@
       <c r="N29" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O29" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>2504015</v>
       </c>
@@ -5621,8 +6869,11 @@
       <c r="N30" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O30" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>2308857</v>
       </c>
@@ -5665,8 +6916,11 @@
       <c r="N31" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O31" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>2503007</v>
       </c>
@@ -5709,8 +6963,11 @@
       <c r="N32" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O32" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>2406944</v>
       </c>
@@ -5753,8 +7010,11 @@
       <c r="N33" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O33" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>2504016</v>
       </c>
@@ -5797,8 +7057,11 @@
       <c r="N34" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O34" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>2002570</v>
       </c>
@@ -5841,8 +7104,11 @@
       <c r="N35" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O35" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>2211745</v>
       </c>
@@ -5883,8 +7149,11 @@
       <c r="N36" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O36" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>2302772</v>
       </c>
@@ -5927,8 +7196,11 @@
       <c r="N37" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O37" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>1906479</v>
       </c>
@@ -5971,8 +7243,11 @@
       <c r="N38" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O38" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>2309862</v>
       </c>
@@ -6015,8 +7290,11 @@
       <c r="N39" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O39" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>2503011</v>
       </c>
@@ -6059,8 +7337,11 @@
       <c r="N40" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O40" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>2002568</v>
       </c>
@@ -6089,7 +7370,7 @@
         <v>196</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>88</v>
+        <v>1296</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>22</v>
@@ -6103,8 +7384,11 @@
       <c r="N41" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O41" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>2207710</v>
       </c>
@@ -6147,8 +7431,11 @@
       <c r="N42" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O42" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>2302776</v>
       </c>
@@ -6191,8 +7478,11 @@
       <c r="N43" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O43" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>2010582</v>
       </c>
@@ -6235,8 +7525,11 @@
       <c r="N44" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O44" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>2411992</v>
       </c>
@@ -6279,8 +7572,11 @@
       <c r="N45" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O45" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>2408961</v>
       </c>
@@ -6323,8 +7619,11 @@
       <c r="N46" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O46" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>2405929</v>
       </c>
@@ -6367,8 +7666,11 @@
       <c r="N47" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O47" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>2001558</v>
       </c>
@@ -6411,8 +7713,11 @@
       <c r="N48" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O48" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>2410984</v>
       </c>
@@ -6455,8 +7760,11 @@
       <c r="N49" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O49" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>2111647</v>
       </c>
@@ -6499,8 +7807,11 @@
       <c r="N50" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O50" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>2602008</v>
       </c>
@@ -6541,8 +7852,11 @@
       <c r="N51" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O51" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>2505021</v>
       </c>
@@ -6585,8 +7899,11 @@
       <c r="N52" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O52" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>2208719</v>
       </c>
@@ -6629,8 +7946,11 @@
       <c r="N53" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O53" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>1906471</v>
       </c>
@@ -6673,8 +7993,11 @@
       <c r="N54" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O54" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>2305815</v>
       </c>
@@ -6717,8 +8040,11 @@
       <c r="N55" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O55" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>2303788</v>
       </c>
@@ -6761,8 +8087,11 @@
       <c r="N56" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O56" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>2404919</v>
       </c>
@@ -6805,8 +8134,11 @@
       <c r="N57" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O57" t="s">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>2510035</v>
       </c>
@@ -6849,8 +8181,11 @@
       <c r="N58" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O58" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>2408960</v>
       </c>
@@ -6893,8 +8228,11 @@
       <c r="N59" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O59" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>2506025</v>
       </c>
@@ -6937,8 +8275,11 @@
       <c r="N60" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O60" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>2412101</v>
       </c>
@@ -6981,8 +8322,11 @@
       <c r="N61" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O61" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>2405932</v>
       </c>
@@ -7025,8 +8369,11 @@
       <c r="N62" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O62" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>2409972</v>
       </c>
@@ -7069,8 +8416,11 @@
       <c r="N63" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O63" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>2503009</v>
       </c>
@@ -7113,8 +8463,11 @@
       <c r="N64" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O64" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>2407958</v>
       </c>
@@ -7157,8 +8510,11 @@
       <c r="N65" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O65" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>2109628</v>
       </c>
@@ -7201,8 +8557,11 @@
       <c r="N66" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O66" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>2409971</v>
       </c>
@@ -7245,8 +8604,11 @@
       <c r="N67" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O67" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>2211740</v>
       </c>
@@ -7289,8 +8651,11 @@
       <c r="N68" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O68" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>2107616</v>
       </c>
@@ -7333,8 +8698,11 @@
       <c r="N69" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O69" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>1704008</v>
       </c>
@@ -7377,8 +8745,11 @@
       <c r="N70" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O70" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>2304804</v>
       </c>
@@ -7421,8 +8792,11 @@
       <c r="N71" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O71" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>2502004</v>
       </c>
@@ -7465,8 +8839,11 @@
       <c r="N72" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O72" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>1907491</v>
       </c>
@@ -7509,8 +8886,11 @@
       <c r="N73" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O73" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>1912546</v>
       </c>
@@ -7553,8 +8933,11 @@
       <c r="N74" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O74" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>2409977</v>
       </c>
@@ -7595,8 +8978,11 @@
       <c r="N75" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O75" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>1901417</v>
       </c>
@@ -7639,8 +9025,11 @@
       <c r="N76" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O76" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>2308852</v>
       </c>
@@ -7683,8 +9072,11 @@
       <c r="N77" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O77" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>2309866</v>
       </c>
@@ -7727,8 +9119,11 @@
       <c r="N78" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O78" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>2205698</v>
       </c>
@@ -7771,8 +9166,11 @@
       <c r="N79" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O79" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>2304809</v>
       </c>
@@ -7815,8 +9213,11 @@
       <c r="N80" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O80" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>2212751</v>
       </c>
@@ -7859,8 +9260,11 @@
       <c r="N81" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O81" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>2512041</v>
       </c>
@@ -7903,8 +9307,11 @@
       <c r="N82" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O82" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>1907485</v>
       </c>
@@ -7947,8 +9354,11 @@
       <c r="N83" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O83" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>2210730</v>
       </c>
@@ -7991,8 +9401,11 @@
       <c r="N84" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O84" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>2211737</v>
       </c>
@@ -8035,8 +9448,11 @@
       <c r="N85" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O85" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>2305820</v>
       </c>
@@ -8079,8 +9495,11 @@
       <c r="N86" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O86" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>2506023</v>
       </c>
@@ -8123,8 +9542,11 @@
       <c r="N87" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O87" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>2510034</v>
       </c>
@@ -8167,8 +9589,11 @@
       <c r="N88" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O88" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>1910535</v>
       </c>
@@ -8211,8 +9636,11 @@
       <c r="N89" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O89" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>2406942</v>
       </c>
@@ -8255,8 +9683,11 @@
       <c r="N90" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O90" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>2201657</v>
       </c>
@@ -8299,8 +9730,11 @@
       <c r="N91" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O91" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>1907487</v>
       </c>
@@ -8343,8 +9777,11 @@
       <c r="N92" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O92" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>1805334</v>
       </c>
@@ -8387,8 +9824,11 @@
       <c r="N93" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O93" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>1907486</v>
       </c>
@@ -8431,8 +9871,11 @@
       <c r="N94" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O94" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>2411989</v>
       </c>
@@ -8475,8 +9918,11 @@
       <c r="N95" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O95" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>2510033</v>
       </c>
@@ -8519,8 +9965,11 @@
       <c r="N96" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O96" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>2309864</v>
       </c>
@@ -8563,8 +10012,11 @@
       <c r="N97" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O97" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>2310876</v>
       </c>
@@ -8607,8 +10059,11 @@
       <c r="N98" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O98" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>2406939</v>
       </c>
@@ -8651,8 +10106,11 @@
       <c r="N99" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O99" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>2209727</v>
       </c>
@@ -8695,8 +10153,11 @@
       <c r="N100" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O100" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>2401903</v>
       </c>
@@ -8739,8 +10200,11 @@
       <c r="N101" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O101" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>2405931</v>
       </c>
@@ -8783,8 +10247,11 @@
       <c r="N102" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O102" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>2504017</v>
       </c>
@@ -8827,8 +10294,11 @@
       <c r="N103" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O103" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>1709016</v>
       </c>
@@ -8871,8 +10341,11 @@
       <c r="N104" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O104" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>2409974</v>
       </c>
@@ -8915,8 +10388,11 @@
       <c r="N105" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O105" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>1910528</v>
       </c>
@@ -8959,8 +10435,11 @@
       <c r="N106" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O106" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>1703007</v>
       </c>
@@ -9003,8 +10482,11 @@
       <c r="N107" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O107" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>2310875</v>
       </c>
@@ -9047,8 +10529,11 @@
       <c r="N108" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O108" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>1807359</v>
       </c>
@@ -9091,8 +10576,11 @@
       <c r="N109" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O109" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>1709017</v>
       </c>
@@ -9135,8 +10623,11 @@
       <c r="N110" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O110" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>2308850</v>
       </c>
@@ -9179,8 +10670,11 @@
       <c r="N111" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O111" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>1710020</v>
       </c>
@@ -9223,8 +10717,11 @@
       <c r="N112" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O112" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>2204690</v>
       </c>
@@ -9267,8 +10764,11 @@
       <c r="N113" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O113" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>2407948</v>
       </c>
@@ -9311,8 +10811,11 @@
       <c r="N114" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O114" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>1901415</v>
       </c>
@@ -9355,8 +10858,11 @@
       <c r="N115" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O115" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>2303792</v>
       </c>
@@ -9399,8 +10905,11 @@
       <c r="N116" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O116" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>1907500</v>
       </c>
@@ -9443,8 +10952,11 @@
       <c r="N117" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O117" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>2509031</v>
       </c>
@@ -9487,8 +10999,11 @@
       <c r="N118" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O118" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>2210731</v>
       </c>
@@ -9531,8 +11046,11 @@
       <c r="N119" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O119" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>2404918</v>
       </c>
@@ -9575,8 +11093,11 @@
       <c r="N120" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O120" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>2003576</v>
       </c>
@@ -9619,8 +11140,11 @@
       <c r="N121" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O121" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>2508030</v>
       </c>
@@ -9663,8 +11187,11 @@
       <c r="N122" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O122" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>2509032</v>
       </c>
@@ -9707,8 +11234,11 @@
       <c r="N123" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O123" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>2505018</v>
       </c>
@@ -9751,8 +11281,11 @@
       <c r="N124" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O124" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>1906467</v>
       </c>
@@ -9795,8 +11328,11 @@
       <c r="N125" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O125" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>2301757</v>
       </c>
@@ -9839,8 +11375,11 @@
       <c r="N126" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O126" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>2410985</v>
       </c>
@@ -9883,8 +11422,11 @@
       <c r="N127" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O127" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>2307835</v>
       </c>
@@ -9927,8 +11469,11 @@
       <c r="N128" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O128" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>1904442</v>
       </c>
@@ -9971,8 +11516,11 @@
       <c r="N129" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O129" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>2212754</v>
       </c>
@@ -10015,8 +11563,11 @@
       <c r="N130" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O130" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>1802308</v>
       </c>
@@ -10059,8 +11610,11 @@
       <c r="N131" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O131" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>1907498</v>
       </c>
@@ -10103,8 +11657,11 @@
       <c r="N132" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O132" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>2301761</v>
       </c>
@@ -10147,8 +11704,11 @@
       <c r="N133" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O133" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>2107621</v>
       </c>
@@ -10191,8 +11751,11 @@
       <c r="N134" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O134" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>2304810</v>
       </c>
@@ -10235,8 +11798,11 @@
       <c r="N135" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O135" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>2307842</v>
       </c>
@@ -10279,8 +11845,11 @@
       <c r="N136" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O136" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>2408966</v>
       </c>
@@ -10321,8 +11890,11 @@
       <c r="N137" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O137" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>1701001</v>
       </c>
@@ -10365,8 +11937,11 @@
       <c r="N138" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O138" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>2409973</v>
       </c>
@@ -10407,8 +11982,11 @@
       <c r="N139" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O139" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>2002561</v>
       </c>
@@ -10451,8 +12029,11 @@
       <c r="N140" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O140" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>1908521</v>
       </c>
@@ -10495,8 +12076,11 @@
       <c r="N141" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O141" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>1712298</v>
       </c>
@@ -10539,8 +12123,11 @@
       <c r="N142" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O142" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>2206704</v>
       </c>
@@ -10583,8 +12170,11 @@
       <c r="N143" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O143" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>2412993</v>
       </c>
@@ -10625,8 +12215,11 @@
       <c r="N144" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O144" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>2111640</v>
       </c>
@@ -10669,8 +12262,11 @@
       <c r="N145" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O145" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>1806355</v>
       </c>
@@ -10713,8 +12309,11 @@
       <c r="N146" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O146" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>2410987</v>
       </c>
@@ -10757,8 +12356,11 @@
       <c r="N147" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O147" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>2108624</v>
       </c>
@@ -10801,8 +12403,11 @@
       <c r="N148" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O148" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>1901413</v>
       </c>
@@ -10845,8 +12450,11 @@
       <c r="N149" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O149" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>2309867</v>
       </c>
@@ -10875,7 +12483,7 @@
         <v>432</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>591</v>
+        <v>1293</v>
       </c>
       <c r="K150" s="2" t="s">
         <v>22</v>
@@ -10889,8 +12497,11 @@
       <c r="N150" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O150" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>2411990</v>
       </c>
@@ -10933,8 +12544,11 @@
       <c r="N151" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O151" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>2101589</v>
       </c>
@@ -10977,8 +12591,11 @@
       <c r="N152" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O152" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>1710286</v>
       </c>
@@ -11021,8 +12638,11 @@
       <c r="N153" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O153" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>1703246</v>
       </c>
@@ -11065,8 +12685,11 @@
       <c r="N154" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O154" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>2001548</v>
       </c>
@@ -11109,8 +12732,11 @@
       <c r="N155" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O155" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>2302774</v>
       </c>
@@ -11153,8 +12779,11 @@
       <c r="N156" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O156" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>1101023</v>
       </c>
@@ -11197,8 +12826,11 @@
       <c r="N157" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O157" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>1710281</v>
       </c>
@@ -11241,8 +12873,11 @@
       <c r="N158" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O158" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>1706267</v>
       </c>
@@ -11285,8 +12920,11 @@
       <c r="N159" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O159" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>2001557</v>
       </c>
@@ -11329,8 +12967,11 @@
       <c r="N160" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O160" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>1405151</v>
       </c>
@@ -11373,8 +13014,11 @@
       <c r="N161" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O161" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>1905450</v>
       </c>
@@ -11403,7 +13047,7 @@
         <v>642</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>591</v>
+        <v>1293</v>
       </c>
       <c r="K162" s="2" t="s">
         <v>22</v>
@@ -11417,8 +13061,11 @@
       <c r="N162" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O162" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>2107620</v>
       </c>
@@ -11461,8 +13108,11 @@
       <c r="N163" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O163" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>2310879</v>
       </c>
@@ -11505,8 +13155,11 @@
       <c r="N164" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O164" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>1101027</v>
       </c>
@@ -11549,8 +13202,11 @@
       <c r="N165" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O165" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>1101066</v>
       </c>
@@ -11593,8 +13249,11 @@
       <c r="N166" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O166" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>1101102</v>
       </c>
@@ -11637,8 +13296,11 @@
       <c r="N167" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O167" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>2601001</v>
       </c>
@@ -11681,8 +13343,11 @@
       <c r="N168" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O168" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>2110638</v>
       </c>
@@ -11725,8 +13390,11 @@
       <c r="N169" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O169" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>1609212</v>
       </c>
@@ -11769,8 +13437,11 @@
       <c r="N170" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O170" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>2601005</v>
       </c>
@@ -11813,8 +13484,11 @@
       <c r="N171" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O171" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>1101019</v>
       </c>
@@ -11857,8 +13531,11 @@
       <c r="N172" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O172" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>1101069</v>
       </c>
@@ -11901,8 +13578,11 @@
       <c r="N173" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O173" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>1803322</v>
       </c>
@@ -11945,8 +13625,11 @@
       <c r="N174" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O174" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>1101036</v>
       </c>
@@ -11989,8 +13672,11 @@
       <c r="N175" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O175" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>2310886</v>
       </c>
@@ -12033,8 +13719,11 @@
       <c r="N176" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O176" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>2412998</v>
       </c>
@@ -12077,8 +13766,11 @@
       <c r="N177" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O177" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>2503006</v>
       </c>
@@ -12121,8 +13813,11 @@
       <c r="N178" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O178" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>2205694</v>
       </c>
@@ -12165,8 +13860,11 @@
       <c r="N179" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O179" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>2209724</v>
       </c>
@@ -12195,7 +13893,7 @@
         <v>702</v>
       </c>
       <c r="J180" s="2" t="s">
-        <v>591</v>
+        <v>1294</v>
       </c>
       <c r="K180" s="2" t="s">
         <v>22</v>
@@ -12209,8 +13907,11 @@
       <c r="N180" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O180" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>2410986</v>
       </c>
@@ -12253,8 +13954,11 @@
       <c r="N181" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O181" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>1805343</v>
       </c>
@@ -12297,8 +14001,11 @@
       <c r="N182" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O182" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>1901435</v>
       </c>
@@ -12341,8 +14048,11 @@
       <c r="N183" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O183" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>1611229</v>
       </c>
@@ -12385,8 +14095,11 @@
       <c r="N184" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O184" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>2301756</v>
       </c>
@@ -12427,8 +14140,11 @@
       <c r="N185" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O185" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>1501167</v>
       </c>
@@ -12471,8 +14187,11 @@
       <c r="N186" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O186" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>2203676</v>
       </c>
@@ -12515,8 +14234,11 @@
       <c r="N187" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O187" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>2111641</v>
       </c>
@@ -12559,8 +14281,11 @@
       <c r="N188" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O188" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>2311895</v>
       </c>
@@ -12603,8 +14328,11 @@
       <c r="N189" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O189" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>1412165</v>
       </c>
@@ -12647,8 +14375,11 @@
       <c r="N190" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O190" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>1806348</v>
       </c>
@@ -12691,8 +14422,11 @@
       <c r="N191" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O191" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>1307138</v>
       </c>
@@ -12735,8 +14469,11 @@
       <c r="N192" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O192" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>2309871</v>
       </c>
@@ -12779,8 +14516,11 @@
       <c r="N193" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O193" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>1101099</v>
       </c>
@@ -12823,8 +14563,11 @@
       <c r="N194" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O194" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>1803319</v>
       </c>
@@ -12853,7 +14596,7 @@
         <v>196</v>
       </c>
       <c r="J195" s="2" t="s">
-        <v>591</v>
+        <v>1295</v>
       </c>
       <c r="K195" s="2" t="s">
         <v>22</v>
@@ -12867,8 +14610,11 @@
       <c r="N195" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O195" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>1911542</v>
       </c>
@@ -12911,8 +14657,11 @@
       <c r="N196" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O196" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>1101013</v>
       </c>
@@ -12955,8 +14704,11 @@
       <c r="N197" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O197" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>1411163</v>
       </c>
@@ -12999,8 +14751,11 @@
       <c r="N198" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O198" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>2408964</v>
       </c>
@@ -13043,8 +14798,11 @@
       <c r="N199" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O199" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>2412994</v>
       </c>
@@ -13087,8 +14845,11 @@
       <c r="N200" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O200" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>2303782</v>
       </c>
@@ -13131,8 +14892,11 @@
       <c r="N201" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O201" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>1711292</v>
       </c>
@@ -13175,8 +14939,11 @@
       <c r="N202" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O202" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>1408157</v>
       </c>
@@ -13219,8 +14986,11 @@
       <c r="N203" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O203" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>1101090</v>
       </c>
@@ -13263,8 +15033,11 @@
       <c r="N204" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O204" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>1901429</v>
       </c>
@@ -13307,8 +15080,11 @@
       <c r="N205" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O205" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>1101053</v>
       </c>
@@ -13351,8 +15127,11 @@
       <c r="N206" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O206" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>2308855</v>
       </c>
@@ -13395,8 +15174,11 @@
       <c r="N207" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O207" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>2212748</v>
       </c>
@@ -13439,8 +15221,11 @@
       <c r="N208" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O208" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>2203679</v>
       </c>
@@ -13483,8 +15268,11 @@
       <c r="N209" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O209" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>1704256</v>
       </c>
@@ -13527,8 +15315,11 @@
       <c r="N210" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O210" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>2406934</v>
       </c>
@@ -13571,8 +15362,11 @@
       <c r="N211" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O211" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>1301123</v>
       </c>
@@ -13615,8 +15409,11 @@
       <c r="N212" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O212" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>2412996</v>
       </c>
@@ -13659,8 +15456,11 @@
       <c r="N213" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O213" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>2306822</v>
       </c>
@@ -13689,7 +15489,7 @@
         <v>824</v>
       </c>
       <c r="J214" s="2" t="s">
-        <v>591</v>
+        <v>1294</v>
       </c>
       <c r="K214" s="2" t="s">
         <v>22</v>
@@ -13703,8 +15503,11 @@
       <c r="N214" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O214" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>2305813</v>
       </c>
@@ -13747,8 +15550,11 @@
       <c r="N215" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O215" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>1101071</v>
       </c>
@@ -13791,8 +15597,11 @@
       <c r="N216" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O216" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>1309141</v>
       </c>
@@ -13835,8 +15644,11 @@
       <c r="N217" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O217" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>1509189</v>
       </c>
@@ -13879,8 +15691,11 @@
       <c r="N218" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O218" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>2003575</v>
       </c>
@@ -13909,7 +15724,7 @@
         <v>839</v>
       </c>
       <c r="J219" s="2" t="s">
-        <v>591</v>
+        <v>1294</v>
       </c>
       <c r="K219" s="2" t="s">
         <v>22</v>
@@ -13923,8 +15738,11 @@
       <c r="N219" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O219" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>1803321</v>
       </c>
@@ -13967,8 +15785,11 @@
       <c r="N220" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O220" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>1101042</v>
       </c>
@@ -14011,8 +15832,11 @@
       <c r="N221" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O221" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>1805344</v>
       </c>
@@ -14055,8 +15879,11 @@
       <c r="N222" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O222" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>1101047</v>
       </c>
@@ -14099,8 +15926,11 @@
       <c r="N223" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O223" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>1407155</v>
       </c>
@@ -14143,8 +15973,11 @@
       <c r="N224" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O224" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>2501001</v>
       </c>
@@ -14187,8 +16020,11 @@
       <c r="N225" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O225" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>2404924</v>
       </c>
@@ -14231,8 +16067,11 @@
       <c r="N226" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O226" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>2206706</v>
       </c>
@@ -14275,8 +16114,11 @@
       <c r="N227" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O227" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>2406936</v>
       </c>
@@ -14319,8 +16161,11 @@
       <c r="N228" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O228" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>2110636</v>
       </c>
@@ -14363,8 +16208,11 @@
       <c r="N229" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O229" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>1509190</v>
       </c>
@@ -14393,7 +16241,7 @@
         <v>875</v>
       </c>
       <c r="J230" s="2" t="s">
-        <v>591</v>
+        <v>1293</v>
       </c>
       <c r="K230" s="2" t="s">
         <v>22</v>
@@ -14407,8 +16255,11 @@
       <c r="N230" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O230" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>1101034</v>
       </c>
@@ -14451,8 +16302,11 @@
       <c r="N231" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O231" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>2307844</v>
       </c>
@@ -14495,8 +16349,11 @@
       <c r="N232" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O232" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>2307841</v>
       </c>
@@ -14539,8 +16396,11 @@
       <c r="N233" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O233" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>1101009</v>
       </c>
@@ -14583,8 +16443,11 @@
       <c r="N234" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O234" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>1101062</v>
       </c>
@@ -14627,8 +16490,11 @@
       <c r="N235" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O235" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>1101097</v>
       </c>
@@ -14671,8 +16537,11 @@
       <c r="N236" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O236" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>2103601</v>
       </c>
@@ -14715,8 +16584,11 @@
       <c r="N237" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O237" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>2301766</v>
       </c>
@@ -14759,8 +16631,11 @@
       <c r="N238" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O238" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>1908505</v>
       </c>
@@ -14803,8 +16678,11 @@
       <c r="N239" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O239" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>2406940</v>
       </c>
@@ -14847,8 +16725,11 @@
       <c r="N240" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O240" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>2401902</v>
       </c>
@@ -14891,8 +16772,11 @@
       <c r="N241" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O241" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>1911543</v>
       </c>
@@ -14935,8 +16819,11 @@
       <c r="N242" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O242" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>2307839</v>
       </c>
@@ -14979,8 +16866,11 @@
       <c r="N243" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O243" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>1710280</v>
       </c>
@@ -15023,8 +16913,11 @@
       <c r="N244" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O244" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A245" s="2">
         <v>2406941</v>
       </c>
@@ -15067,8 +16960,11 @@
       <c r="N245" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O245" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A246" s="2">
         <v>1901432</v>
       </c>
@@ -15111,8 +17007,11 @@
       <c r="N246" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O246" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A247" s="2">
         <v>2404917</v>
       </c>
@@ -15155,8 +17054,11 @@
       <c r="N247" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O247" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A248" s="2">
         <v>2406933</v>
       </c>
@@ -15199,8 +17101,11 @@
       <c r="N248" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O248" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A249" s="2">
         <v>2109626</v>
       </c>
@@ -15243,8 +17148,11 @@
       <c r="N249" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O249" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A250" s="2">
         <v>2303796</v>
       </c>
@@ -15287,8 +17195,11 @@
       <c r="N250" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O250" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A251" s="2">
         <v>2303794</v>
       </c>
@@ -15331,8 +17242,11 @@
       <c r="N251" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O251" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A252" s="2">
         <v>2407952</v>
       </c>
@@ -15375,8 +17289,11 @@
       <c r="N252" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O252" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A253" s="2">
         <v>1709278</v>
       </c>
@@ -15419,8 +17336,11 @@
       <c r="N253" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O253" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A254" s="2">
         <v>1809388</v>
       </c>
@@ -15449,7 +17369,7 @@
         <v>952</v>
       </c>
       <c r="J254" s="2" t="s">
-        <v>591</v>
+        <v>1294</v>
       </c>
       <c r="K254" s="2" t="s">
         <v>22</v>
@@ -15463,8 +17383,11 @@
       <c r="N254" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O254" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A255" s="2">
         <v>1101065</v>
       </c>
@@ -15507,8 +17430,11 @@
       <c r="N255" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O255" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A256" s="2">
         <v>1908517</v>
       </c>
@@ -15551,8 +17477,11 @@
       <c r="N256" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O256" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A257" s="2">
         <v>1306135</v>
       </c>
@@ -15595,8 +17524,11 @@
       <c r="N257" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O257" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A258" s="2">
         <v>1612233</v>
       </c>
@@ -15637,8 +17569,11 @@
       <c r="N258" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O258" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A259" s="2">
         <v>1101028</v>
       </c>
@@ -15681,8 +17616,11 @@
       <c r="N259" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O259" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A260" s="2">
         <v>2407951</v>
       </c>
@@ -15725,8 +17663,11 @@
       <c r="N260" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O260" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A261" s="2">
         <v>1506177</v>
       </c>
@@ -15769,8 +17710,11 @@
       <c r="N261" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O261" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A262" s="2">
         <v>2109629</v>
       </c>
@@ -15813,8 +17757,11 @@
       <c r="N262" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O262" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A263" s="2">
         <v>1907484</v>
       </c>
@@ -15857,8 +17804,11 @@
       <c r="N263" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O263" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A264" s="2">
         <v>1302127</v>
       </c>
@@ -15901,8 +17851,11 @@
       <c r="N264" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O264" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A265" s="2">
         <v>1101025</v>
       </c>
@@ -15945,8 +17898,11 @@
       <c r="N265" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O265" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A266" s="2">
         <v>1803315</v>
       </c>
@@ -15989,8 +17945,11 @@
       <c r="N266" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O266" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A267" s="2">
         <v>1601194</v>
       </c>
@@ -16033,8 +17992,11 @@
       <c r="N267" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O267" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A268" s="2">
         <v>1509184</v>
       </c>
@@ -16063,7 +18025,7 @@
         <v>997</v>
       </c>
       <c r="J268" s="2" t="s">
-        <v>591</v>
+        <v>1294</v>
       </c>
       <c r="K268" s="2" t="s">
         <v>22</v>
@@ -16077,8 +18039,11 @@
       <c r="N268" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O268" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A269" s="2">
         <v>1101072</v>
       </c>
@@ -16121,8 +18086,11 @@
       <c r="N269" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O269" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A270" s="2">
         <v>2303799</v>
       </c>
@@ -16165,8 +18133,11 @@
       <c r="N270" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O270" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A271" s="2">
         <v>1610217</v>
       </c>
@@ -16209,8 +18180,11 @@
       <c r="N271" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O271" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A272" s="2">
         <v>1101085</v>
       </c>
@@ -16239,7 +18213,7 @@
         <v>356</v>
       </c>
       <c r="J272" s="2" t="s">
-        <v>591</v>
+        <v>1293</v>
       </c>
       <c r="K272" s="2" t="s">
         <v>22</v>
@@ -16253,8 +18227,11 @@
       <c r="N272" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O272" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A273" s="2">
         <v>1806357</v>
       </c>
@@ -16297,8 +18274,11 @@
       <c r="N273" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O273" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A274" s="2">
         <v>1905451</v>
       </c>
@@ -16341,8 +18321,11 @@
       <c r="N274" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O274" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A275" s="2">
         <v>1101038</v>
       </c>
@@ -16385,8 +18368,11 @@
       <c r="N275" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O275" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A276" s="2">
         <v>2205696</v>
       </c>
@@ -16429,8 +18415,11 @@
       <c r="N276" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O276" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A277" s="2">
         <v>1605199</v>
       </c>
@@ -16473,8 +18462,11 @@
       <c r="N277" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O277" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A278" s="2">
         <v>2505020</v>
       </c>
@@ -16517,8 +18509,11 @@
       <c r="N278" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O278" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A279" s="2">
         <v>2303784</v>
       </c>
@@ -16561,8 +18556,11 @@
       <c r="N279" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O279" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A280" s="2">
         <v>2408965</v>
       </c>
@@ -16605,8 +18603,11 @@
       <c r="N280" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O280" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A281" s="2">
         <v>2406935</v>
       </c>
@@ -16649,8 +18650,11 @@
       <c r="N281" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O281" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A282" s="2">
         <v>2201658</v>
       </c>
@@ -16693,8 +18697,11 @@
       <c r="N282" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O282" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A283" s="2">
         <v>1610222</v>
       </c>
@@ -16737,8 +18744,11 @@
       <c r="N283" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O283" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A284" s="2">
         <v>2203684</v>
       </c>
@@ -16781,8 +18791,11 @@
       <c r="N284" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O284" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A285" s="2">
         <v>1101060</v>
       </c>
@@ -16825,8 +18838,11 @@
       <c r="N285" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O285" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A286" s="2">
         <v>2109625</v>
       </c>
@@ -16869,8 +18885,11 @@
       <c r="N286" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O286" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A287" s="2">
         <v>1101103</v>
       </c>
@@ -16913,8 +18932,11 @@
       <c r="N287" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O287" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A288" s="2">
         <v>1101048</v>
       </c>
@@ -16957,8 +18979,11 @@
       <c r="N288" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O288" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A289" s="2">
         <v>2310878</v>
       </c>
@@ -17001,8 +19026,11 @@
       <c r="N289" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O289" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A290" s="2">
         <v>1101056</v>
       </c>
@@ -17045,8 +19073,11 @@
       <c r="N290" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O290" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A291" s="2">
         <v>2208721</v>
       </c>
@@ -17075,7 +19106,7 @@
         <v>356</v>
       </c>
       <c r="J291" s="2" t="s">
-        <v>591</v>
+        <v>1293</v>
       </c>
       <c r="K291" s="2" t="s">
         <v>22</v>
@@ -17089,8 +19120,11 @@
       <c r="N291" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O291" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A292" s="2">
         <v>1101011</v>
       </c>
@@ -17133,8 +19167,11 @@
       <c r="N292" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O292" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A293" s="2">
         <v>1807364</v>
       </c>
@@ -17177,8 +19214,11 @@
       <c r="N293" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O293" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A294" s="2">
         <v>1711290</v>
       </c>
@@ -17221,8 +19261,11 @@
       <c r="N294" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O294" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A295" s="2">
         <v>1811399</v>
       </c>
@@ -17265,8 +19308,11 @@
       <c r="N295" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O295" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A296" s="2">
         <v>1401144</v>
       </c>
@@ -17309,8 +19355,11 @@
       <c r="N296" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O296" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A297" s="2">
         <v>1101087</v>
       </c>
@@ -17353,8 +19402,11 @@
       <c r="N297" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O297" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A298" s="2">
         <v>2209726</v>
       </c>
@@ -17397,8 +19449,11 @@
       <c r="N298" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O298" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A299" s="2">
         <v>2409969</v>
       </c>
@@ -17427,7 +19482,7 @@
         <v>200</v>
       </c>
       <c r="J299" s="2" t="s">
-        <v>591</v>
+        <v>1296</v>
       </c>
       <c r="K299" s="2" t="s">
         <v>22</v>
@@ -17441,8 +19496,11 @@
       <c r="N299" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O299" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A300" s="2">
         <v>1303129</v>
       </c>
@@ -17485,8 +19543,11 @@
       <c r="N300" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O300" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A301" s="2">
         <v>1806350</v>
       </c>
@@ -17515,7 +19576,7 @@
         <v>839</v>
       </c>
       <c r="J301" s="2" t="s">
-        <v>591</v>
+        <v>1294</v>
       </c>
       <c r="K301" s="2" t="s">
         <v>22</v>
@@ -17529,8 +19590,11 @@
       <c r="N301" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O301" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A302" s="2">
         <v>2403911</v>
       </c>
@@ -17573,8 +19637,11 @@
       <c r="N302" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O302" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A303" s="2">
         <v>1101050</v>
       </c>
@@ -17617,8 +19684,11 @@
       <c r="N303" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O303" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A304" s="2">
         <v>1803323</v>
       </c>
@@ -17647,7 +19717,7 @@
         <v>1105</v>
       </c>
       <c r="J304" s="2" t="s">
-        <v>536</v>
+        <v>1296</v>
       </c>
       <c r="K304" s="2" t="s">
         <v>680</v>
@@ -17661,8 +19731,11 @@
       <c r="N304" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O304" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A305" s="2">
         <v>2203686</v>
       </c>
@@ -17705,8 +19778,11 @@
       <c r="N305" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O305" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A306" s="2">
         <v>1101024</v>
       </c>
@@ -17749,8 +19825,11 @@
       <c r="N306" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O306" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A307" s="2">
         <v>2412997</v>
       </c>
@@ -17791,8 +19870,11 @@
       <c r="N307" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O307" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A308" s="2">
         <v>1509186</v>
       </c>
@@ -17835,8 +19917,11 @@
       <c r="N308" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O308" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A309" s="2">
         <v>2301762</v>
       </c>
@@ -17879,8 +19964,11 @@
       <c r="N309" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O309" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A310" s="2">
         <v>2309863</v>
       </c>
@@ -17923,8 +20011,11 @@
       <c r="N310" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O310" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A311" s="2">
         <v>2406945</v>
       </c>
@@ -17967,8 +20058,11 @@
       <c r="N311" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O311" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A312" s="2">
         <v>2105607</v>
       </c>
@@ -18011,8 +20105,11 @@
       <c r="N312" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O312" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A313" s="2">
         <v>2408967</v>
       </c>
@@ -18055,8 +20152,11 @@
       <c r="N313" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O313" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="314" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A314" s="2">
         <v>2302781</v>
       </c>
@@ -18099,8 +20199,11 @@
       <c r="N314" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O314" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="315" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A315" s="2">
         <v>1101100</v>
       </c>
@@ -18143,8 +20246,11 @@
       <c r="N315" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O315" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="316" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A316" s="2">
         <v>1101022</v>
       </c>
@@ -18187,8 +20293,11 @@
       <c r="N316" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O316" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="317" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A317" s="2">
         <v>1101067</v>
       </c>
@@ -18231,8 +20340,11 @@
       <c r="N317" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O317" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A318" s="2">
         <v>1101017</v>
       </c>
@@ -18275,8 +20387,11 @@
       <c r="N318" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O318" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="319" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A319" s="2">
         <v>1811409</v>
       </c>
@@ -18319,8 +20434,11 @@
       <c r="N319" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O319" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A320" s="2">
         <v>1504172</v>
       </c>
@@ -18363,8 +20481,11 @@
       <c r="N320" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O320" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A321" s="2">
         <v>2211746</v>
       </c>
@@ -18407,8 +20528,11 @@
       <c r="N321" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O321" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A322" s="2">
         <v>1404148</v>
       </c>
@@ -18451,8 +20575,11 @@
       <c r="N322" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O322" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A323" s="2">
         <v>2308856</v>
       </c>
@@ -18495,8 +20622,11 @@
       <c r="N323" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O323" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A324" s="2">
         <v>1611225</v>
       </c>
@@ -18525,7 +20655,7 @@
         <v>1160</v>
       </c>
       <c r="J324" s="2" t="s">
-        <v>591</v>
+        <v>1293</v>
       </c>
       <c r="K324" s="2" t="s">
         <v>22</v>
@@ -18539,8 +20669,11 @@
       <c r="N324" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O324" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A325" s="2">
         <v>1610219</v>
       </c>
@@ -18583,8 +20716,11 @@
       <c r="N325" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O325" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A326" s="2">
         <v>2308848</v>
       </c>
@@ -18627,8 +20763,11 @@
       <c r="N326" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O326" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A327" s="2">
         <v>2008580</v>
       </c>
@@ -18671,8 +20810,11 @@
       <c r="N327" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O327" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A328" s="2">
         <v>1609213</v>
       </c>
@@ -18701,7 +20843,7 @@
         <v>997</v>
       </c>
       <c r="J328" s="2" t="s">
-        <v>591</v>
+        <v>1294</v>
       </c>
       <c r="K328" s="2" t="s">
         <v>22</v>
@@ -18715,8 +20857,11 @@
       <c r="N328" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O328" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A329" s="2">
         <v>1406152</v>
       </c>
@@ -18759,8 +20904,11 @@
       <c r="N329" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O329" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A330" s="2">
         <v>1212122</v>
       </c>
@@ -18803,8 +20951,11 @@
       <c r="N330" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O330" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A331" s="2">
         <v>2211736</v>
       </c>
@@ -18847,8 +20998,11 @@
       <c r="N331" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O331" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2">
         <v>2303797</v>
       </c>
@@ -18891,8 +21045,11 @@
       <c r="N332" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O332" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="333" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2">
         <v>2210732</v>
       </c>
@@ -18935,8 +21092,11 @@
       <c r="N333" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O333" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="2">
         <v>2301760</v>
       </c>
@@ -18979,8 +21139,11 @@
       <c r="N334" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O334" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2">
         <v>2512042</v>
       </c>
@@ -19023,8 +21186,11 @@
       <c r="N335" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O335" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2">
         <v>2409979</v>
       </c>
@@ -19067,8 +21233,11 @@
       <c r="N336" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O336" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2">
         <v>2512045</v>
       </c>
@@ -19111,8 +21280,11 @@
       <c r="N337" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O337" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2">
         <v>2309869</v>
       </c>
@@ -19155,8 +21327,11 @@
       <c r="N338" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O338" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="2">
         <v>2305819</v>
       </c>
@@ -19199,8 +21374,11 @@
       <c r="N339" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O339" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2">
         <v>2302767</v>
       </c>
@@ -19243,8 +21421,11 @@
       <c r="N340" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O340" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="2">
         <v>2302769</v>
       </c>
@@ -19287,8 +21468,11 @@
       <c r="N341" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O341" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2">
         <v>2507028</v>
       </c>
@@ -19331,8 +21515,11 @@
       <c r="N342" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O342" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="2">
         <v>2307834</v>
       </c>
@@ -19375,8 +21562,11 @@
       <c r="N343" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O343" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2">
         <v>2311889</v>
       </c>
@@ -19419,8 +21609,11 @@
       <c r="N344" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O344" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="2">
         <v>2511040</v>
       </c>
@@ -19463,8 +21656,11 @@
       <c r="N345" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O345" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="2">
         <v>2103600</v>
       </c>
@@ -19507,8 +21703,11 @@
       <c r="N346" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O346" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="2">
         <v>2502005</v>
       </c>
@@ -19551,8 +21750,11 @@
       <c r="N347" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O347" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2">
         <v>2601006</v>
       </c>
@@ -19595,8 +21797,11 @@
       <c r="N348" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O348" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="2">
         <v>2602007</v>
       </c>
@@ -19639,8 +21844,11 @@
       <c r="N349" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O349" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2">
         <v>2311894</v>
       </c>
@@ -19683,8 +21891,11 @@
       <c r="N350" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O350" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="2">
         <v>2307833</v>
       </c>
@@ -19727,8 +21938,11 @@
       <c r="N351" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O351" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2">
         <v>2310873</v>
       </c>
@@ -19771,8 +21985,11 @@
       <c r="N352" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O352" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="2">
         <v>2307837</v>
       </c>
@@ -19815,8 +22032,11 @@
       <c r="N353" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O353" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="2">
         <v>2504014</v>
       </c>
@@ -19859,8 +22079,11 @@
       <c r="N354" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O354" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="355" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="2">
         <v>2201660</v>
       </c>
@@ -19903,8 +22126,11 @@
       <c r="N355" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O355" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="2">
         <v>2302770</v>
       </c>
@@ -19947,8 +22173,11 @@
       <c r="N356" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O356" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="2">
         <v>2110639</v>
       </c>
@@ -19991,8 +22220,11 @@
       <c r="N357" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O357" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="2">
         <v>2103598</v>
       </c>
@@ -20033,8 +22265,11 @@
       <c r="N358" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O358" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="359" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="2">
         <v>2511038</v>
       </c>
@@ -20077,8 +22312,11 @@
       <c r="N359" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O359" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="360" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2">
         <v>2402910</v>
       </c>
@@ -20121,8 +22359,11 @@
       <c r="N360" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O360" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="361" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="2">
         <v>2402906</v>
       </c>
@@ -20165,8 +22406,11 @@
       <c r="N361" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O361" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="362" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="2">
         <v>2301763</v>
       </c>
@@ -20209,8 +22453,11 @@
       <c r="N362" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O362" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="363" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="2">
         <v>2310877</v>
       </c>
@@ -20253,8 +22500,11 @@
       <c r="N363" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O363" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="364" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2">
         <v>2308849</v>
       </c>
@@ -20296,6 +22546,82 @@
       </c>
       <c r="N364" s="2" t="s">
         <v>24</v>
+      </c>
+      <c r="O364" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O364" xr:uid="{87F23702-AA52-4900-9029-87698A4EA02C}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Ortigas &amp; Company, Limited Partnership"/>
+        <filter val="Ortigas Commercial Corporation"/>
+        <filter val="Ortigas Land Corporation"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{124541A9-AB1A-4815-9869-E3D48ED258BC}">
+  <dimension ref="A2:A11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="32.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>1292</v>
       </c>
     </row>
   </sheetData>
